--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\AllStar-Towing-and-Recovery\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE1BEF8-3E30-4253-91AA-710C2352EA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65B8CB76-8BD4-43B1-9EAC-2DA08FFCEB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -89,13 +89,10 @@
     <t>Alert Driving: Big Three</t>
   </si>
   <si>
-    <t>Camera Event Management Orientation for Drivers</t>
+    <t>Dangers of Distracted Driving</t>
   </si>
   <si>
-    <t>Colton Flint</t>
-  </si>
-  <si>
-    <t>Mark Yazel</t>
+    <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
     <t>Allstar Towing &amp; Recovery Inc</t>
@@ -111,6 +108,9 @@
   </si>
   <si>
     <t>Clint Fiser</t>
+  </si>
+  <si>
+    <t>Colton Flint</t>
   </si>
   <si>
     <t>David Petty (DJ)</t>
@@ -149,6 +149,9 @@
     <t>Leo Buckles</t>
   </si>
   <si>
+    <t>Mark Yazel</t>
+  </si>
+  <si>
     <t>Michael Beary</t>
   </si>
   <si>
@@ -159,9 +162,6 @@
   </si>
   <si>
     <t>William (Billy) Moore</t>
-  </si>
-  <si>
-    <t>Dangers of Distracted Driving</t>
   </si>
 </sst>
 </file>
@@ -535,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K7400"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -550,50 +550,50 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2">
         <v>5487</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -611,18 +611,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3">
         <v>5483</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
         <v>10</v>
@@ -640,18 +640,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4">
         <v>5473</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -669,18 +669,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5">
         <v>5484</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
@@ -698,18 +698,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6">
         <v>5490</v>
       </c>
       <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
         <v>17</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -727,9 +727,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7">
         <v>5488</v>
@@ -738,7 +738,7 @@
         <v>24</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
         <v>10</v>
@@ -756,9 +756,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8">
         <v>5581</v>
@@ -767,7 +767,7 @@
         <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
         <v>10</v>
@@ -785,9 +785,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9">
         <v>5491</v>
@@ -796,7 +796,7 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -814,9 +814,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10">
         <v>5489</v>
@@ -825,7 +825,7 @@
         <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
         <v>10</v>
@@ -843,9 +843,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11">
         <v>5474</v>
@@ -854,7 +854,7 @@
         <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G11" t="s">
         <v>10</v>
@@ -872,9 +872,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12">
         <v>5476</v>
@@ -883,7 +883,7 @@
         <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G12" t="s">
         <v>10</v>
@@ -901,9 +901,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13">
         <v>5660</v>
@@ -912,7 +912,7 @@
         <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -930,9 +930,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14">
         <v>5471</v>
@@ -941,7 +941,7 @@
         <v>31</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G14" t="s">
         <v>10</v>
@@ -959,9 +959,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15">
         <v>5478</v>
@@ -970,7 +970,7 @@
         <v>32</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G15" t="s">
         <v>10</v>
@@ -988,9 +988,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>5479</v>
@@ -999,7 +999,7 @@
         <v>33</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -1019,7 +1019,7 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17">
         <v>5661</v>
@@ -1028,7 +1028,7 @@
         <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G17" t="s">
         <v>10</v>
@@ -1048,7 +1048,7 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18">
         <v>5485</v>
@@ -1057,7 +1057,7 @@
         <v>35</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G18" t="s">
         <v>10</v>
@@ -1077,16 +1077,16 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C19">
         <v>5472</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -1106,16 +1106,16 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20">
         <v>5475</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -1135,16 +1135,16 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C21">
         <v>5486</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G21" t="s">
         <v>10</v>
@@ -1164,16 +1164,16 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C22">
         <v>5481</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C23">
         <v>5482</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
@@ -1222,13 +1222,13 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C24">
         <v>5487</v>
       </c>
       <c r="D24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
@@ -1251,13 +1251,13 @@
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C25">
         <v>5483</v>
       </c>
       <c r="D25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F25" t="s">
         <v>15</v>
@@ -1280,13 +1280,13 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C26">
         <v>5473</v>
       </c>
       <c r="D26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F26" t="s">
         <v>15</v>
@@ -1317,13 +1317,13 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C28">
         <v>5484</v>
       </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F28" t="s">
         <v>15</v>
@@ -1346,13 +1346,13 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C29">
         <v>5490</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F29" t="s">
         <v>15</v>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C30">
         <v>5488</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C31">
         <v>5581</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C32">
         <v>5491</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C33">
         <v>5489</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C34">
         <v>5474</v>
@@ -1520,7 +1520,7 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C35">
         <v>5476</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C36">
         <v>5660</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C37">
         <v>5471</v>
@@ -1607,7 +1607,7 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C38">
         <v>5478</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C39">
         <v>5479</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C40">
         <v>5661</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C41">
         <v>5485</v>
@@ -1723,13 +1723,13 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C42">
         <v>5472</v>
       </c>
       <c r="D42" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F42" t="s">
         <v>15</v>
@@ -1752,13 +1752,13 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C43">
         <v>5475</v>
       </c>
       <c r="D43" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F43" t="s">
         <v>15</v>
@@ -1781,13 +1781,13 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C44">
         <v>5486</v>
       </c>
       <c r="D44" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F44" t="s">
         <v>15</v>
@@ -1810,13 +1810,13 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C45">
         <v>5481</v>
       </c>
       <c r="D45" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F45" t="s">
         <v>15</v>
@@ -1839,13 +1839,13 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C46">
         <v>5482</v>
       </c>
       <c r="D46" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F46" t="s">
         <v>15</v>
@@ -1868,16 +1868,16 @@
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C47">
         <v>5487</v>
       </c>
       <c r="D47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G47" t="s">
         <v>10</v>
@@ -1897,16 +1897,16 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C48">
         <v>5483</v>
       </c>
       <c r="D48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F48" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G48" t="s">
         <v>10</v>
@@ -1926,16 +1926,16 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C49">
         <v>5473</v>
       </c>
       <c r="D49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F49" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G49" t="s">
         <v>13</v>
@@ -1955,16 +1955,16 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C50">
         <v>5484</v>
       </c>
       <c r="D50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F50" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G50" t="s">
         <v>10</v>
@@ -1984,16 +1984,16 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C51">
         <v>5490</v>
       </c>
       <c r="D51" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F51" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G51" t="s">
         <v>10</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C52">
         <v>5488</v>
@@ -2022,7 +2022,7 @@
         <v>24</v>
       </c>
       <c r="F52" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G52" t="s">
         <v>13</v>
@@ -2042,7 +2042,7 @@
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C53">
         <v>5581</v>
@@ -2051,7 +2051,7 @@
         <v>25</v>
       </c>
       <c r="F53" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G53" t="s">
         <v>10</v>
@@ -2071,7 +2071,7 @@
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C54">
         <v>5491</v>
@@ -2080,7 +2080,7 @@
         <v>26</v>
       </c>
       <c r="F54" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G54" t="s">
         <v>13</v>
@@ -2100,7 +2100,7 @@
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C55">
         <v>5489</v>
@@ -2109,7 +2109,7 @@
         <v>27</v>
       </c>
       <c r="F55" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G55" t="s">
         <v>10</v>
@@ -2129,7 +2129,7 @@
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C56">
         <v>5474</v>
@@ -2138,7 +2138,7 @@
         <v>28</v>
       </c>
       <c r="F56" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G56" t="s">
         <v>10</v>
@@ -2158,7 +2158,7 @@
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C57">
         <v>5476</v>
@@ -2167,7 +2167,7 @@
         <v>29</v>
       </c>
       <c r="F57" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G57" t="s">
         <v>10</v>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C58">
         <v>5660</v>
@@ -2196,7 +2196,7 @@
         <v>30</v>
       </c>
       <c r="F58" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G58" t="s">
         <v>13</v>
@@ -2216,7 +2216,7 @@
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C59">
         <v>5471</v>
@@ -2225,7 +2225,7 @@
         <v>31</v>
       </c>
       <c r="F59" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G59" t="s">
         <v>13</v>
@@ -2245,7 +2245,7 @@
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C60">
         <v>5478</v>
@@ -2254,7 +2254,7 @@
         <v>32</v>
       </c>
       <c r="F60" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G60" t="s">
         <v>10</v>
@@ -2274,7 +2274,7 @@
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C61">
         <v>5479</v>
@@ -2283,7 +2283,7 @@
         <v>33</v>
       </c>
       <c r="F61" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G61" t="s">
         <v>13</v>
@@ -2303,7 +2303,7 @@
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C62">
         <v>5661</v>
@@ -2312,7 +2312,7 @@
         <v>34</v>
       </c>
       <c r="F62" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G62" t="s">
         <v>10</v>
@@ -2332,7 +2332,7 @@
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C63">
         <v>5485</v>
@@ -2341,7 +2341,7 @@
         <v>35</v>
       </c>
       <c r="F63" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G63" t="s">
         <v>10</v>
@@ -2361,16 +2361,16 @@
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C64">
         <v>5472</v>
       </c>
       <c r="D64" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F64" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G64" t="s">
         <v>13</v>
@@ -2390,16 +2390,16 @@
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C65">
         <v>5475</v>
       </c>
       <c r="D65" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F65" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G65" t="s">
         <v>13</v>
@@ -2419,16 +2419,16 @@
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C66">
         <v>5486</v>
       </c>
       <c r="D66" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F66" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G66" t="s">
         <v>10</v>
@@ -2448,16 +2448,16 @@
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C67">
         <v>5481</v>
       </c>
       <c r="D67" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F67" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G67" t="s">
         <v>10</v>
@@ -2477,16 +2477,16 @@
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C68">
         <v>5482</v>
       </c>
       <c r="D68" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F68" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G68" t="s">
         <v>13</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\AllStar-Towing-and-Recovery\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65B8CB76-8BD4-43B1-9EAC-2DA08FFCEB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5131BFC5-B4E8-42A7-AA1A-A22244B0E53F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1938,10 +1938,10 @@
         <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H49" s="2">
-        <v>0</v>
+        <v>7.0254629629629634E-3</v>
       </c>
       <c r="I49" s="1">
         <v>46237.636342592596</v>
@@ -2025,10 +2025,10 @@
         <v>16</v>
       </c>
       <c r="G52" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H52" s="2">
-        <v>0</v>
+        <v>8.4259259259259253E-3</v>
       </c>
       <c r="I52" s="1">
         <v>46237.637731481482</v>
@@ -2092,7 +2092,7 @@
         <v>46237.638425925928</v>
       </c>
       <c r="J54" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>11</v>
@@ -2199,10 +2199,10 @@
         <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H58" s="2">
-        <v>0</v>
+        <v>6.898148148148148E-3</v>
       </c>
       <c r="I58" s="1">
         <v>46237.640509259261</v>
@@ -2228,10 +2228,10 @@
         <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H59" s="2">
-        <v>0</v>
+        <v>1.238425925925926E-2</v>
       </c>
       <c r="I59" s="1">
         <v>46237.641203703701</v>
@@ -2286,10 +2286,10 @@
         <v>16</v>
       </c>
       <c r="G61" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H61" s="2">
-        <v>0</v>
+        <v>6.2500000000000003E-3</v>
       </c>
       <c r="I61" s="1">
         <v>46237.641898148147</v>
@@ -2382,7 +2382,7 @@
         <v>46237.643287037034</v>
       </c>
       <c r="J64" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K64" s="1" t="s">
         <v>11</v>
@@ -2402,16 +2402,16 @@
         <v>16</v>
       </c>
       <c r="G65" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H65" s="2">
-        <v>0</v>
+        <v>7.1412037037037034E-3</v>
       </c>
       <c r="I65" s="1">
         <v>46237.643287037034</v>
       </c>
       <c r="J65" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" s="1" t="s">
         <v>11</v>
@@ -2498,7 +2498,7 @@
         <v>46237.644675925927</v>
       </c>
       <c r="J68" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K68" s="1" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\AllStar-Towing-and-Recovery\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5131BFC5-B4E8-42A7-AA1A-A22244B0E53F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5FF2F7C-1672-4C99-88AC-CF825A367D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
